--- a/data/XY/data_set_3&4/data_set_3&4_mechanism_oriented_descriptors.xlsx
+++ b/data/XY/data_set_3&4/data_set_3&4_mechanism_oriented_descriptors.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\0_doctor_reserch\1_nitroxide\paper\250604_3rd_submit_M06\github\data\XY\data_set_3&amp;4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\0_doctor_reserch\1_nitroxide\paper\250604_3rd_submit_M06\github\Mechanism_Oriented_Reaction_Descriptors_for_living_radical_polymerization\data\XY\data_set_3&amp;4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81504791-DBF9-41EF-9C0D-2DA3A3E2703B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D3D249-A146-4C4A-8FEF-C3BF9A856F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -72,6 +72,16 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
+    <t>Buried_volume_N_dormant_3_5</t>
+  </si>
+  <si>
+    <t>Buried_volume_N_mediator_3_5</t>
+  </si>
+  <si>
+    <t>Conversion</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>7 (24)</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -81,16 +91,6 @@
   </si>
   <si>
     <t>13 (28)</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Buried_volume_N_dormant_3_5</t>
-  </si>
-  <si>
-    <t>Buried_volume_N_mediator_3_5</t>
-  </si>
-  <si>
-    <t>Conversion</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -516,7 +516,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -540,7 +540,7 @@
         <v>10</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>11</v>
@@ -558,7 +558,7 @@
         <v>12</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.15">
@@ -982,7 +982,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S22"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
@@ -999,7 +999,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -1023,7 +1023,7 @@
         <v>10</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>11</v>
@@ -1400,7 +1400,7 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B8">
         <v>1.4206649851390021</v>
@@ -1459,7 +1459,7 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B9">
         <v>1.4212818158268259</v>
@@ -1754,7 +1754,7 @@
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B14">
         <v>1.419261075348718</v>
@@ -2222,65 +2222,6 @@
       </c>
       <c r="S21" s="2">
         <v>66</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A22" s="1">
-        <v>21</v>
-      </c>
-      <c r="B22">
-        <v>1.4298265629089431</v>
-      </c>
-      <c r="C22">
-        <v>1.43498745639117</v>
-      </c>
-      <c r="D22">
-        <v>122.84058852259869</v>
-      </c>
-      <c r="E22">
-        <v>0.91584746552366758</v>
-      </c>
-      <c r="F22">
-        <v>0.84967270778978754</v>
-      </c>
-      <c r="G22">
-        <v>-7.3960544565899999</v>
-      </c>
-      <c r="H22">
-        <v>0.48000883228199998</v>
-      </c>
-      <c r="I22">
-        <v>7.8760632888720004</v>
-      </c>
-      <c r="J22">
-        <v>-0.44724000000000003</v>
-      </c>
-      <c r="K22">
-        <v>1.271093230254964</v>
-      </c>
-      <c r="L22">
-        <v>128.05254040079009</v>
-      </c>
-      <c r="M22">
-        <v>0.8499697167349981</v>
-      </c>
-      <c r="N22">
-        <v>0.59231736861721951</v>
-      </c>
-      <c r="O22">
-        <v>-6.876317002135</v>
-      </c>
-      <c r="P22">
-        <v>-0.43973000000000001</v>
-      </c>
-      <c r="Q22">
-        <v>-32.954942670050123</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22" s="2">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
